--- a/data/trans_orig/Q17B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q17B-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de veces que ha consultado al médico en las 2 últimas semanas</t>
+          <t>Número medio de veces que la población ha tenido una consulta médica en las 2 últimas semanas (tasa de respuesta: 99,19%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,14</t>
+          <t>0,04; 0,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,24</t>
+          <t>0,17; 0,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,33</t>
+          <t>0,15; 0,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,37</t>
+          <t>0,25; 0,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,39</t>
+          <t>0,28; 0,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,27 +891,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,63</t>
+          <t>0,27; 0,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,24</t>
+          <t>0,17; 0,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,3</t>
+          <t>0,23; 0,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,35</t>
+          <t>0,25; 0,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,48</t>
+          <t>0,24; 0,49</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,32</t>
+          <t>0,22; 0,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,35</t>
+          <t>0,25; 0,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,32</t>
+          <t>0,24; 0,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,34</t>
+          <t>0,27; 0,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,24</t>
+          <t>0,15; 0,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,26</t>
+          <t>0,17; 0,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,45</t>
+          <t>0,28; 0,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,17 +1156,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,43</t>
+          <t>0,3; 0,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,47</t>
+          <t>0,35; 0,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,42</t>
+          <t>0,29; 0,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,34</t>
+          <t>0,27; 0,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,4</t>
+          <t>0,3; 0,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,53</t>
+          <t>0,34; 0,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,55</t>
+          <t>0,32; 0,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,38</t>
+          <t>0,26; 0,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1306,12 +1306,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,65</t>
+          <t>0,43; 0,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,4</t>
+          <t>0,3; 0,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,49</t>
+          <t>0,38; 0,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,56</t>
+          <t>0,41; 0,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,77</t>
+          <t>0,46; 0,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,63</t>
+          <t>0,45; 0,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,59</t>
+          <t>0,42; 0,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,22 +1436,22 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,55</t>
+          <t>0,44; 0,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,84</t>
+          <t>0,5; 0,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 0,69</t>
+          <t>0,51; 0,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,39</t>
+          <t>0,1; 0,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,62</t>
+          <t>0,49; 0,61</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,4</t>
+          <t>0,16; 0,4</t>
         </is>
       </c>
     </row>
@@ -1556,57 +1556,57 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,57</t>
+          <t>0,4; 0,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,71</t>
+          <t>0,49; 0,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,69</t>
+          <t>0,45; 0,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,42</t>
+          <t>0,29; 0,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,82</t>
+          <t>0,53; 0,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,7</t>
+          <t>0,55; 0,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,75</t>
+          <t>0,49; 0,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,43</t>
+          <t>0,34; 0,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,68</t>
+          <t>0,5; 0,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,67</t>
+          <t>0,54; 0,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,67</t>
+          <t>0,5; 0,68</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,27</t>
+          <t>0,22; 0,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,46</t>
+          <t>0,39; 0,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">

--- a/data/trans_orig/Q17B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q17B-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,19 +683,19 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0,22</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,23</t>
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,16</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,21</t>
+          <t>0,13; 0,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,15</t>
+          <t>0,04; 0,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,25</t>
+          <t>0,16; 0,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,36</t>
+          <t>0,23; 0,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,32</t>
+          <t>0,18; 0,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,26</t>
+          <t>0,19; 0,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,2</t>
+          <t>0,12; 0,24</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,25</t>
         </is>
       </c>
     </row>
@@ -866,52 +866,52 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,24</t>
+          <t>0,15; 0,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,29</t>
+          <t>0,15; 0,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,36</t>
+          <t>0,25; 0,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,4</t>
+          <t>0,29; 0,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,52</t>
+          <t>0,32; 0,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,64</t>
+          <t>0,24; 0,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,25</t>
+          <t>0,18; 0,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,31</t>
+          <t>0,23; 0,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,36</t>
+          <t>0,24; 0,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,49</t>
+          <t>0,2; 0,3</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,28</t>
+          <t>0,15; 0,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,33</t>
+          <t>0,21; 0,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,25</t>
+          <t>0,15; 0,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,35</t>
+          <t>0,26; 0,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,36</t>
+          <t>0,25; 0,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,33</t>
+          <t>0,24; 0,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,35</t>
+          <t>0,27; 0,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,28</t>
+          <t>0,2; 0,28</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,28</t>
         </is>
       </c>
     </row>
@@ -1141,37 +1141,37 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,25</t>
+          <t>0,18; 0,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,44</t>
+          <t>0,29; 0,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,26</t>
+          <t>0,2; 0,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,42</t>
+          <t>0,3; 0,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,46</t>
+          <t>0,34; 0,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,42</t>
+          <t>0,29; 0,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,37</t>
+          <t>0,28; 0,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,41</t>
+          <t>0,3; 0,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,29</t>
+          <t>0,25; 0,31</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,53</t>
+          <t>0,34; 0,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,55</t>
+          <t>0,32; 0,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,37</t>
+          <t>0,25; 0,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,49</t>
+          <t>0,37; 0,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,62</t>
+          <t>0,43; 0,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,41</t>
+          <t>0,32; 0,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,49</t>
+          <t>0,38; 0,48</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,55</t>
+          <t>0,4; 0,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,37</t>
+          <t>0,3; 0,39</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,38</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,74</t>
+          <t>0,46; 0,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1431,27 +1431,27 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,51</t>
+          <t>0,31; 0,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,55</t>
+          <t>0,43; 0,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,86</t>
+          <t>0,5; 0,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,67</t>
+          <t>0,51; 0,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,4</t>
+          <t>0,34; 0,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,7</t>
+          <t>0,5; 0,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,4</t>
+          <t>0,34; 0,45</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,27 +1523,27 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0,39</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0,57</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0,6</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0,58</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>0,38</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0,6</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>0,58</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
         </is>
       </c>
     </row>
@@ -1556,37 +1556,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,57</t>
+          <t>0,41; 0,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,73</t>
+          <t>0,48; 0,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,7</t>
+          <t>0,46; 0,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,42</t>
+          <t>0,31; 0,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,8</t>
+          <t>0,52; 0,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,7</t>
+          <t>0,54; 0,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,74</t>
+          <t>0,5; 0,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,69</t>
+          <t>0,5; 0,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,41</t>
+          <t>0,34; 0,42</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,14 +1663,14 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>0,33</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>0,31</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0,35</t>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,29</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,35</t>
+          <t>0,3; 0,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,26</t>
+          <t>0,22; 0,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>0,39; 0,44</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
           <t>0,39; 0,45</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,39; 0,45</t>
-        </is>
-      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,35</t>
+          <t>0,31; 0,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,3</t>
+          <t>0,27; 0,3</t>
         </is>
       </c>
     </row>
